--- a/Database/ECONO 50 CORDLESS.xlsx
+++ b/Database/ECONO 50 CORDLESS.xlsx
@@ -8,23 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NGODING\BOOS\BOOS\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4009277-B577-43AE-80F0-F196B5A26E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01862645-ED25-4D3D-A8EA-C12F06B3997C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{A9B6EDBF-62BA-4076-BF36-63B390B83C8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Factory" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Row Labels</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -867,9 +863,6 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
       <c r="B1">
         <v>610</v>
       </c>
